--- a/output/yearly_surface_area_iteration_99_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_99_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449762758093</v>
+        <v>10.84497631153283</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907174536493</v>
+        <v>37.78907186984276</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.079562621772997</v>
+        <v>6.280240064066846</v>
       </c>
       <c r="C2" t="n">
-        <v>7.550621593362218</v>
+        <v>7.982590583230815</v>
       </c>
       <c r="D2" t="n">
-        <v>24.36108753318035</v>
+        <v>31.07722357793278</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.40991287648544</v>
+        <v>20.24854640009046</v>
       </c>
       <c r="C3" t="n">
-        <v>33.01617529382023</v>
+        <v>24.81858196335937</v>
       </c>
       <c r="D3" t="n">
-        <v>66.46431957750906</v>
+        <v>93.31511928865933</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.8422260237193</v>
+        <v>40.24085664937251</v>
       </c>
       <c r="C4" t="n">
-        <v>66.95322993422398</v>
+        <v>42.28289187420587</v>
       </c>
       <c r="D4" t="n">
-        <v>88.35631163450869</v>
+        <v>110.1295122192945</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.23402547317179</v>
+        <v>50.16730768701202</v>
       </c>
       <c r="C5" t="n">
-        <v>99.59830459583894</v>
+        <v>64.81989217289566</v>
       </c>
       <c r="D5" t="n">
-        <v>65.31076602501908</v>
+        <v>70.66129101316419</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.43153668817465</v>
+        <v>49.34853010167018</v>
       </c>
       <c r="C6" t="n">
-        <v>109.5247556334784</v>
+        <v>87.26558993509049</v>
       </c>
       <c r="D6" t="n">
-        <v>45.60512610537709</v>
+        <v>45.44411948188061</v>
       </c>
     </row>
     <row r="7">
@@ -850,10 +850,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.32069700858599</v>
+        <v>35.69241953559704</v>
       </c>
       <c r="C7" t="n">
-        <v>100.489731511295</v>
+        <v>97.25585457350601</v>
       </c>
       <c r="D7" t="n">
         <v>38.50709020367265</v>
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.02212253330794</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="C8" t="n">
-        <v>67.00918955336604</v>
+        <v>75.52094214918588</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
-        <v>38.82812170296133</v>
+        <v>45.15155866601504</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.698051072893134</v>
+        <v>7.683820798839431</v>
       </c>
       <c r="C21" t="n">
-        <v>94.30112564294089</v>
+        <v>93.1663271859281</v>
       </c>
       <c r="D21" t="n">
-        <v>8.660307457004775</v>
+        <v>7.683820798839431</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.108434215823654</v>
+        <v>8.463646958311752</v>
       </c>
       <c r="C2" t="n">
-        <v>8.493099389439157</v>
+        <v>10.29067943591507</v>
       </c>
       <c r="D2" t="n">
-        <v>28.46675643234051</v>
+        <v>32.20917868092936</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64062358698343</v>
+        <v>20.55288818840697</v>
       </c>
       <c r="C3" t="n">
-        <v>30.92996142229576</v>
+        <v>28.19579406596839</v>
       </c>
       <c r="D3" t="n">
-        <v>69.52246367623788</v>
+        <v>95.48478171504479</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.77466535857552</v>
+        <v>39.06668639509333</v>
       </c>
       <c r="C4" t="n">
-        <v>74.80230282967722</v>
+        <v>51.66349118828415</v>
       </c>
       <c r="D4" t="n">
-        <v>98.59201319898594</v>
+        <v>127.3464217086708</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.47379289718628</v>
+        <v>55.29693944170161</v>
       </c>
       <c r="C5" t="n">
-        <v>110.274810879523</v>
+        <v>71.22579594310611</v>
       </c>
       <c r="D5" t="n">
-        <v>80.38059328520761</v>
+        <v>91.52342972840891</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.28690098048088</v>
+        <v>57.88188114698346</v>
       </c>
       <c r="C6" t="n">
-        <v>133.1927292874605</v>
+        <v>94.10837143369076</v>
       </c>
       <c r="D6" t="n">
-        <v>53.97747052719389</v>
+        <v>55.18502020341747</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.90255460203486</v>
+        <v>46.53189593818607</v>
       </c>
       <c r="C7" t="n">
-        <v>127.6183658227471</v>
+        <v>111.8681874035155</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>42.63926629084747</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.36697801940583</v>
+        <v>28.62285431731576</v>
       </c>
       <c r="C8" t="n">
-        <v>99.13688317484291</v>
+        <v>100.5555086074795</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.87031149204818</v>
+        <v>13.64531134132641</v>
       </c>
       <c r="C9" t="n">
-        <v>59.57343244140068</v>
+        <v>68.33749419721195</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>38.29306920414684</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.881623479248708</v>
+        <v>7.866467941310658</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4463081651393</v>
+        <v>101.2807747443747</v>
       </c>
       <c r="D21" t="n">
-        <v>9.852029349060885</v>
+        <v>8.84977643397449</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.221556185990289</v>
+        <v>9.567131377885167</v>
       </c>
       <c r="C2" t="n">
-        <v>8.449902490452297</v>
+        <v>8.52255182056656</v>
       </c>
       <c r="D2" t="n">
-        <v>23.80149134175967</v>
+        <v>27.76284332839555</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.31450342272425</v>
+        <v>23.88101290580366</v>
       </c>
       <c r="C3" t="n">
-        <v>31.66136346195963</v>
+        <v>33.55122779263475</v>
       </c>
       <c r="D3" t="n">
-        <v>74.27903130331367</v>
+        <v>97.61026549473912</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.58773238414112</v>
+        <v>38.7220929509027</v>
       </c>
       <c r="C4" t="n">
-        <v>75.00650635216057</v>
+        <v>59.64019128528948</v>
       </c>
       <c r="D4" t="n">
-        <v>108.2151041960132</v>
+        <v>142.0363126073158</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.52288028239862</v>
+        <v>56.3768619163731</v>
       </c>
       <c r="C5" t="n">
-        <v>122.4730261047896</v>
+        <v>81.877758534184</v>
       </c>
       <c r="D5" t="n">
-        <v>92.87333282174828</v>
+        <v>109.9311991830366</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.84162949110934</v>
+        <v>64.92592092495433</v>
       </c>
       <c r="C6" t="n">
-        <v>150.3399346898353</v>
+        <v>101.6756827380252</v>
       </c>
       <c r="D6" t="n">
-        <v>64.44290105446488</v>
+        <v>68.10580173900973</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.06520592577034</v>
+        <v>56.17364014159399</v>
       </c>
       <c r="C7" t="n">
-        <v>155.3458662337898</v>
+        <v>122.2884575363912</v>
       </c>
       <c r="D7" t="n">
-        <v>46.95110220789945</v>
+        <v>47.19064864773568</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.21252483466959</v>
+        <v>38.30288668118931</v>
       </c>
       <c r="C8" t="n">
-        <v>130.6804369122929</v>
+        <v>122.669375645639</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.08437354930299</v>
+        <v>19.85781081380023</v>
       </c>
       <c r="C9" t="n">
-        <v>86.53124265231384</v>
+        <v>92.52186714362787</v>
       </c>
       <c r="D9" t="n">
         <v>36.83124687252333</v>
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>52.10135066437823</v>
+        <v>58.36490101747288</v>
       </c>
       <c r="D10" t="n">
         <v>36.30012136452581</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>38.02701557629594</v>
+        <v>39.98167525545134</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.04940190935184</v>
+        <v>8.034155161559148</v>
       </c>
       <c r="C21" t="n">
-        <v>111.6854514922568</v>
+        <v>109.4653640762434</v>
       </c>
       <c r="D21" t="n">
-        <v>11.06792762535878</v>
+        <v>10.04269395194894</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.167159151629216</v>
+        <v>8.682576696358792</v>
       </c>
       <c r="C2" t="n">
-        <v>5.677446973659304</v>
+        <v>5.726534358871645</v>
       </c>
       <c r="D2" t="n">
-        <v>19.61139214003428</v>
+        <v>22.95915181151591</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.05005343738336</v>
+        <v>27.94544840138546</v>
       </c>
       <c r="C3" t="n">
-        <v>47.43314033068464</v>
+        <v>46.9079053089126</v>
       </c>
       <c r="D3" t="n">
-        <v>80.8420147062036</v>
+        <v>106.2152841224624</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.30472700341079</v>
+        <v>27.08249216935251</v>
       </c>
       <c r="C4" t="n">
-        <v>102.8930498912912</v>
+        <v>74.07482778083033</v>
       </c>
       <c r="D4" t="n">
-        <v>104.5904916719339</v>
+        <v>133.0385948978938</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.56948008838794</v>
+        <v>36.57010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>89.82991493858316</v>
+        <v>60.74563920027141</v>
       </c>
       <c r="D5" t="n">
-        <v>64.35356201337844</v>
+        <v>71.29942702092461</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>34.85793398698726</v>
+      </c>
+      <c r="C6" t="n">
+        <v>80.54356340411259</v>
+      </c>
+      <c r="D6" t="n">
         <v>31.07427833482005</v>
-      </c>
-      <c r="C6" t="n">
-        <v>102.3197092320111</v>
-      </c>
-      <c r="D6" t="n">
-        <v>30.91327171132357</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.97838585497334</v>
+        <v>25.3919226226395</v>
       </c>
       <c r="C7" t="n">
-        <v>91.86605967719103</v>
+        <v>86.23671834103982</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>28.26647990067416</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>63.75469591378786</v>
+        <v>68.17746932141974</v>
       </c>
       <c r="D8" t="n">
         <v>27.12078032981814</v>
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>39.71562162760046</v>
+        <v>44.48593372253571</v>
       </c>
       <c r="D9" t="n">
         <v>27.62343515439249</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.805655012288137</v>
+        <v>5.138467484027806</v>
       </c>
       <c r="C2" t="n">
-        <v>3.223077713042279</v>
+        <v>2.855904071653971</v>
       </c>
       <c r="D2" t="n">
-        <v>13.61487716249477</v>
+        <v>15.90823979961531</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.60398012675681</v>
+        <v>29.71259426902972</v>
       </c>
       <c r="C3" t="n">
-        <v>35.02875808752619</v>
+        <v>34.87658719336794</v>
       </c>
       <c r="D3" t="n">
-        <v>78.52509012418113</v>
+        <v>101.2623669545373</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.77917318646925</v>
+        <v>38.96458463385165</v>
       </c>
       <c r="C4" t="n">
-        <v>113.3201922580966</v>
+        <v>97.90282631060468</v>
       </c>
       <c r="D4" t="n">
-        <v>119.6377387349248</v>
+        <v>153.5227607470035</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.78470381979624</v>
+        <v>40.12893741108838</v>
       </c>
       <c r="C5" t="n">
-        <v>137.8864650614645</v>
+        <v>96.11310024576277</v>
       </c>
       <c r="D5" t="n">
-        <v>80.69966128908783</v>
+        <v>93.5114688295087</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.11202671593793</v>
+        <v>41.70071548558752</v>
       </c>
       <c r="C6" t="n">
-        <v>124.4983716186508</v>
+        <v>91.25050386662829</v>
       </c>
       <c r="D6" t="n">
-        <v>38.60133798328035</v>
+        <v>39.84913931537804</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>23.83487076370406</v>
       </c>
       <c r="C7" t="n">
-        <v>115.581157220977</v>
+        <v>103.0049691295753</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>11.34900346109313</v>
       </c>
       <c r="C8" t="n">
-        <v>84.5333860741716</v>
+        <v>86.45270283597411</v>
       </c>
       <c r="D8" t="n">
         <v>28.28906009787184</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>50.69843319500952</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.633849164044945</v>
+        <v>6.158503348740242</v>
       </c>
       <c r="C2" t="n">
-        <v>10.76879056788326</v>
+        <v>9.371763584740052</v>
       </c>
       <c r="D2" t="n">
-        <v>18.31843041354124</v>
+        <v>15.38791351636451</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.91613483897829</v>
+        <v>23.51776625523235</v>
       </c>
       <c r="C3" t="n">
-        <v>22.97289627937536</v>
+        <v>22.12368451520187</v>
       </c>
       <c r="D3" t="n">
-        <v>72.36953201855363</v>
+        <v>92.13702204356315</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.33019569045897</v>
+        <v>47.88572602234242</v>
       </c>
       <c r="C4" t="n">
-        <v>99.85552249435158</v>
+        <v>92.24894128184729</v>
       </c>
       <c r="D4" t="n">
-        <v>128.6354564443468</v>
+        <v>165.2899887301057</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.45429681182157</v>
+        <v>48.62105505282329</v>
       </c>
       <c r="C5" t="n">
-        <v>174.7510913559323</v>
+        <v>139.2609118474101</v>
       </c>
       <c r="D5" t="n">
-        <v>102.6171787863979</v>
+        <v>123.5774922720673</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.46549694719579</v>
+        <v>47.69821221083129</v>
       </c>
       <c r="C6" t="n">
-        <v>169.0972063271749</v>
+        <v>120.2719477518683</v>
       </c>
       <c r="D6" t="n">
-        <v>52.44790760397736</v>
+        <v>56.714583126634</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.3625112492411</v>
+        <v>34.55457394637499</v>
       </c>
       <c r="C7" t="n">
-        <v>147.3809471092354</v>
+        <v>118.3958278890526</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>16.68971097219578</v>
       </c>
       <c r="C8" t="n">
-        <v>116.7445282505095</v>
+        <v>110.736232300519</v>
       </c>
       <c r="D8" t="n">
         <v>29.87458264023044</v>
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>71.66561891460864</v>
+        <v>75.65936857548466</v>
       </c>
       <c r="D9" t="n">
         <v>29.28749751309084</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>42.13661146627311</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.755765805820797</v>
+        <v>3.621667280966483</v>
       </c>
       <c r="C2" t="n">
-        <v>4.948008429403925</v>
+        <v>4.319689898685966</v>
       </c>
       <c r="D2" t="n">
-        <v>12.63116596283946</v>
+        <v>10.64018161862693</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.700150344044</v>
+        <v>24.61732368398877</v>
       </c>
       <c r="C3" t="n">
-        <v>32.85418692261951</v>
+        <v>29.92367002544278</v>
       </c>
       <c r="D3" t="n">
-        <v>72.78186605433729</v>
+        <v>88.21984870361838</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.82267318509238</v>
+        <v>52.76108512163209</v>
       </c>
       <c r="C4" t="n">
-        <v>94.83977347335463</v>
+        <v>87.51397210426492</v>
       </c>
       <c r="D4" t="n">
-        <v>138.3606492026157</v>
+        <v>175.9340973395497</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.03138453546945</v>
+        <v>50.70726892434777</v>
       </c>
       <c r="C5" t="n">
-        <v>203.2954058569083</v>
+        <v>168.4188186635403</v>
       </c>
       <c r="D5" t="n">
-        <v>108.0904222375738</v>
+        <v>133.3704256219292</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.10573531908495</v>
+        <v>41.25794727097221</v>
       </c>
       <c r="C6" t="n">
-        <v>205.0016833668893</v>
+        <v>150.0581730987165</v>
       </c>
       <c r="D6" t="n">
-        <v>51.44161620712438</v>
+        <v>54.98376192404687</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>11.0191362324662</v>
       </c>
       <c r="C7" t="n">
-        <v>154.0283608146906</v>
+        <v>131.810428519881</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>89.37340225610838</v>
+        <v>90.45823346930109</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>32.17187226816797</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.455751918948773</v>
+        <v>4.173409490753191</v>
       </c>
       <c r="C2" t="n">
-        <v>7.081346190732242</v>
+        <v>8.329147522829938</v>
       </c>
       <c r="D2" t="n">
-        <v>15.57640907557989</v>
+        <v>13.54320958008475</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.09927969131594</v>
+        <v>18.6679325962531</v>
       </c>
       <c r="C3" t="n">
-        <v>25.85923452986099</v>
+        <v>23.17415455874596</v>
       </c>
       <c r="D3" t="n">
-        <v>66.57722056349745</v>
+        <v>77.52861620437062</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.78063796025901</v>
+        <v>50.57865997509143</v>
       </c>
       <c r="C4" t="n">
-        <v>89.24970204537328</v>
+        <v>81.86008707550754</v>
       </c>
       <c r="D4" t="n">
-        <v>142.4447196522825</v>
+        <v>179.3034554605247</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.09429850399926</v>
+        <v>62.9791152274329</v>
       </c>
       <c r="C5" t="n">
-        <v>191.5635207911589</v>
+        <v>166.4553232550467</v>
       </c>
       <c r="D5" t="n">
-        <v>130.1061145053086</v>
+        <v>162.0620022785423</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.68562941712533</v>
+        <v>52.00513938936205</v>
       </c>
       <c r="C6" t="n">
-        <v>259.3414187969502</v>
+        <v>203.4318687877986</v>
       </c>
       <c r="D6" t="n">
-        <v>67.66303352439442</v>
+        <v>76.23663622558183</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.30156077611979</v>
+        <v>23.77498415374501</v>
       </c>
       <c r="C7" t="n">
-        <v>217.6279405912074</v>
+        <v>169.7785392339221</v>
       </c>
       <c r="D7" t="n">
-        <v>40.06414206260808</v>
+        <v>41.02232782195297</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>136.4383871977005</v>
+        <v>127.7597374921587</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>61.01561981893925</v>
+        <v>63.23436963053704</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
         <v>24.62714116103124</v>
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.395464398362217</v>
+        <v>3.133738671955819</v>
       </c>
       <c r="C2" t="n">
-        <v>3.620685533262237</v>
+        <v>4.595561003579319</v>
       </c>
       <c r="D2" t="n">
-        <v>11.91154489562655</v>
+        <v>10.0187353218387</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.84264262988003</v>
+        <v>16.97932654494859</v>
       </c>
       <c r="C3" t="n">
-        <v>27.14041528390307</v>
+        <v>27.67055904419635</v>
       </c>
       <c r="D3" t="n">
-        <v>64.30938336668731</v>
+        <v>72.12900383101315</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.09671966329748</v>
+        <v>45.99684343937156</v>
       </c>
       <c r="C4" t="n">
-        <v>80.22645889564085</v>
+        <v>73.5898444149324</v>
       </c>
       <c r="D4" t="n">
-        <v>143.5933644662512</v>
+        <v>178.5632176915226</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.5920856477814</v>
+        <v>69.67954330891737</v>
       </c>
       <c r="C5" t="n">
-        <v>187.6610736667778</v>
+        <v>166.0871678659542</v>
       </c>
       <c r="D5" t="n">
-        <v>145.2004854581033</v>
+        <v>181.2797135891736</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.45419900083034</v>
+        <v>60.98125864929064</v>
       </c>
       <c r="C6" t="n">
-        <v>287.1150613500925</v>
+        <v>233.3791007581433</v>
       </c>
       <c r="D6" t="n">
-        <v>80.74482168348318</v>
+        <v>93.18258334858602</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.98405535702057</v>
+        <v>22.33770551472768</v>
       </c>
       <c r="C7" t="n">
-        <v>273.6818075128833</v>
+        <v>212.2381456948924</v>
       </c>
       <c r="D7" t="n">
-        <v>45.45393695892307</v>
+        <v>46.8912155979404</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>176.3267964212484</v>
+        <v>160.2212253330794</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>34.71459882216722</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>71.44374393344886</v>
+        <v>72.88593131098743</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>25.19655482949439</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.225442119078272</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C2" t="n">
-        <v>4.871432108472673</v>
+        <v>4.689808783187013</v>
       </c>
       <c r="D2" t="n">
-        <v>12.38965602759475</v>
+        <v>23.5776528651914</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.08884031946772</v>
+        <v>13.89173001509237</v>
       </c>
       <c r="C3" t="n">
-        <v>21.10757564130643</v>
+        <v>22.87963024747192</v>
       </c>
       <c r="D3" t="n">
-        <v>59.6215380789088</v>
+        <v>64.86407081958676</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.45559735469531</v>
+        <v>39.39851711912875</v>
       </c>
       <c r="C4" t="n">
-        <v>74.4704721056418</v>
+        <v>71.34360566761571</v>
       </c>
       <c r="D4" t="n">
-        <v>142.6233977344554</v>
+        <v>174.4153336410799</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.19938656608268</v>
+        <v>69.38501899764334</v>
       </c>
       <c r="C5" t="n">
-        <v>170.2841393016093</v>
+        <v>152.4899621621358</v>
       </c>
       <c r="D5" t="n">
-        <v>158.3804483876167</v>
+        <v>195.8095796120264</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.51711296936016</v>
+        <v>73.78128521726055</v>
       </c>
       <c r="C6" t="n">
-        <v>292.6295382048468</v>
+        <v>246.7023988524768</v>
       </c>
       <c r="D6" t="n">
-        <v>98.53605357984388</v>
+        <v>119.3864113226376</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.71616140694821</v>
+        <v>39.58504918293564</v>
       </c>
       <c r="C7" t="n">
-        <v>330.6938601939041</v>
+        <v>265.776774998288</v>
       </c>
       <c r="D7" t="n">
-        <v>54.49681506274045</v>
+        <v>58.09001166028376</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>11.51590057081509</v>
       </c>
       <c r="C8" t="n">
-        <v>250.2622160280756</v>
+        <v>207.9537987135594</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>124.8046769023757</v>
+        <v>120.2562397886003</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>51.81664383014665</v>
       </c>
       <c r="D10" t="n">
         <v>26.33538216642069</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.866924280578939</v>
+        <v>8.61189086165302</v>
       </c>
       <c r="C2" t="n">
-        <v>5.78347572571796</v>
+        <v>8.884816723433634</v>
       </c>
       <c r="D2" t="n">
-        <v>4.71238898038469</v>
+        <v>5.820782138479339</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.021819433671682</v>
+        <v>3.523492510541802</v>
       </c>
       <c r="C2" t="n">
-        <v>2.767546778271758</v>
+        <v>2.663481521621597</v>
       </c>
       <c r="D2" t="n">
-        <v>9.118472677044375</v>
+        <v>17.35337242026662</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.34471661737765</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="C3" t="n">
-        <v>23.6846633649543</v>
+        <v>24.98547907308132</v>
       </c>
       <c r="D3" t="n">
-        <v>64.88370577367169</v>
+        <v>74.31830121148354</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.73333414400592</v>
+        <v>53.47579745032376</v>
       </c>
       <c r="C4" t="n">
-        <v>104.4883899106923</v>
+        <v>99.12804744550469</v>
       </c>
       <c r="D4" t="n">
-        <v>147.0903497887784</v>
+        <v>179.1758282589726</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.40458753180348</v>
+        <v>43.4914232981337</v>
       </c>
       <c r="C5" t="n">
-        <v>251.0328879759095</v>
+        <v>217.4571164906685</v>
       </c>
       <c r="D5" t="n">
-        <v>143.4578832830652</v>
+        <v>178.5308200172825</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.930861054542</v>
+        <v>24.55351008321273</v>
       </c>
       <c r="C6" t="n">
-        <v>275.1603195554791</v>
+        <v>223.3966901013617</v>
       </c>
       <c r="D6" t="n">
-        <v>79.49702035138549</v>
+        <v>91.77377539299185</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.407867265618931</v>
+        <v>7.60559946480004</v>
       </c>
       <c r="C7" t="n">
-        <v>176.0067466696639</v>
+        <v>146.2431015200134</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>91.96030745679872</v>
+        <v>88.62236526235957</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>25.11801501315464</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>39.49374664644068</v>
       </c>
       <c r="D9" t="n">
         <v>20.07968579496001</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.20713307006285</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.34806277111788</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.975317438673588</v>
+        <v>7.576147033672636</v>
       </c>
       <c r="C2" t="n">
-        <v>5.063854658505048</v>
+        <v>4.498367980858886</v>
       </c>
       <c r="D2" t="n">
-        <v>13.24966701651495</v>
+        <v>15.82773648786708</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.46328710541326</v>
+        <v>18.28014225307561</v>
       </c>
       <c r="C3" t="n">
-        <v>14.8047553800419</v>
+        <v>22.38875639534851</v>
       </c>
       <c r="D3" t="n">
-        <v>7.284567965511333</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39919453147881</v>
+        <v>13.39799892202218</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14872431185967</v>
+        <v>70.14246494470437</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576375827232801</v>
+        <v>1.576235167296727</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.104106314379167</v>
+        <v>5.023603002630929</v>
       </c>
       <c r="C2" t="n">
-        <v>6.92230306264426</v>
+        <v>4.308890673939251</v>
       </c>
       <c r="D2" t="n">
-        <v>24.89417653658637</v>
+        <v>20.14251764803181</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.42878706704438</v>
+        <v>23.08579726536375</v>
       </c>
       <c r="C3" t="n">
-        <v>17.95616551067416</v>
+        <v>19.35515598922587</v>
       </c>
       <c r="D3" t="n">
-        <v>16.65044106402591</v>
+        <v>19.37969968183204</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.4984500963169</v>
+        <v>21.0840136964045</v>
       </c>
       <c r="C4" t="n">
-        <v>23.45787964527329</v>
+        <v>34.66354794154638</v>
       </c>
       <c r="D4" t="n">
-        <v>18.88882582970863</v>
+        <v>19.27170743436488</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44417891332321</v>
+        <v>15.4396700493378</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16226130590846</v>
+        <v>86.13710659104245</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251406087015414</v>
+        <v>3.250456852492168</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.910702016642545</v>
+        <v>5.101161071266427</v>
       </c>
       <c r="C2" t="n">
-        <v>5.234678759043994</v>
+        <v>2.526036843027043</v>
       </c>
       <c r="D2" t="n">
-        <v>25.79542092908494</v>
+        <v>29.21288468756809</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.44213062427633</v>
+        <v>19.87548227247668</v>
       </c>
       <c r="C3" t="n">
-        <v>23.39995653072273</v>
+        <v>17.78435966243097</v>
       </c>
       <c r="D3" t="n">
-        <v>32.70201602846125</v>
+        <v>30.99377502307181</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.50366193447439</v>
+        <v>34.57420890045992</v>
       </c>
       <c r="C4" t="n">
-        <v>36.11849803924015</v>
+        <v>42.80616340056942</v>
       </c>
       <c r="D4" t="n">
-        <v>22.99842171968578</v>
+        <v>24.65757533986289</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.90998231084556</v>
+        <v>17.7450897542611</v>
       </c>
       <c r="C5" t="n">
-        <v>26.99806186678729</v>
+        <v>38.77903431774902</v>
       </c>
       <c r="D5" t="n">
-        <v>29.25608158655496</v>
+        <v>29.59969328304134</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73924883853694</v>
+        <v>16.73097692048468</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1094179150753</v>
+        <v>102.0589592149565</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021774651561082</v>
+        <v>4.18274423012117</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.861033794353459</v>
+        <v>6.613052535806514</v>
       </c>
       <c r="C2" t="n">
-        <v>5.344634501919636</v>
+        <v>3.98295043612931</v>
       </c>
       <c r="D2" t="n">
-        <v>25.03751170140641</v>
+        <v>36.23630776374977</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5585576904542</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="C3" t="n">
-        <v>21.6082669704723</v>
+        <v>13.17014545247096</v>
       </c>
       <c r="D3" t="n">
-        <v>45.03276719380119</v>
+        <v>46.29922173227958</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.08547847019426</v>
+        <v>36.45032876327557</v>
       </c>
       <c r="C4" t="n">
-        <v>48.3068957874643</v>
+        <v>43.75060469205486</v>
       </c>
       <c r="D4" t="n">
-        <v>33.60424216866407</v>
+        <v>34.10198825471721</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.94897448157495</v>
+        <v>34.65569395991241</v>
       </c>
       <c r="C5" t="n">
-        <v>48.84194828627883</v>
+        <v>60.52474596681587</v>
       </c>
       <c r="D5" t="n">
-        <v>30.65507206510666</v>
+        <v>31.48955761371645</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.75348351524281</v>
+        <v>15.01386764104647</v>
       </c>
       <c r="C6" t="n">
-        <v>28.33716573537994</v>
+        <v>37.59504658642736</v>
       </c>
       <c r="D6" t="n">
         <v>38.07806645691679</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06712692532556</v>
+        <v>18.05344634205536</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8664947033144</v>
+        <v>117.7772451838849</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882715019171642</v>
+        <v>6.017815447351785</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.969026041820607</v>
+        <v>6.622870012848982</v>
       </c>
       <c r="C2" t="n">
-        <v>9.097855975255191</v>
+        <v>4.746750150033328</v>
       </c>
       <c r="D2" t="n">
-        <v>21.32552363164922</v>
+        <v>34.29539255245383</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.89096925156637</v>
+        <v>18.64338890364693</v>
       </c>
       <c r="C3" t="n">
-        <v>19.84112110282804</v>
+        <v>13.61193191938202</v>
       </c>
       <c r="D3" t="n">
-        <v>50.84471360294231</v>
+        <v>59.77370897306705</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.96838845148163</v>
+        <v>26.48264432205771</v>
       </c>
       <c r="C4" t="n">
-        <v>42.7551125199486</v>
+        <v>31.53668150352029</v>
       </c>
       <c r="D4" t="n">
-        <v>41.45331506411732</v>
+        <v>42.60195987808609</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.07107104980005</v>
+        <v>27.26804248545517</v>
       </c>
       <c r="C5" t="n">
-        <v>52.7443954106599</v>
+        <v>53.06346341454012</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.25608158655496</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.36354975020759</v>
+        <v>16.82519215538184</v>
       </c>
       <c r="C6" t="n">
-        <v>36.46800022195202</v>
+        <v>45.60512610537709</v>
       </c>
       <c r="D6" t="n">
-        <v>30.5510068084565</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>20.18178755620168</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.062421189151653</v>
+        <v>7.054533562540935</v>
       </c>
       <c r="C21" t="n">
-        <v>66.21019864829675</v>
+        <v>66.13625214882126</v>
       </c>
       <c r="D21" t="n">
-        <v>5.29681589186374</v>
+        <v>4.409083476588084</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.860632883725958</v>
+        <v>6.323436963053706</v>
       </c>
       <c r="C2" t="n">
-        <v>6.71024555852695</v>
+        <v>4.899902791895831</v>
       </c>
       <c r="D2" t="n">
-        <v>24.91184799526281</v>
+        <v>39.69205968269854</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.41406085148068</v>
+        <v>21.50518346152638</v>
       </c>
       <c r="C3" t="n">
-        <v>30.14456325889832</v>
+        <v>16.79279448114169</v>
       </c>
       <c r="D3" t="n">
-        <v>56.83828333736908</v>
+        <v>74.13667788619789</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.62227348023901</v>
+        <v>32.94058072059322</v>
       </c>
       <c r="C4" t="n">
-        <v>47.28587817504762</v>
+        <v>33.20859784385261</v>
       </c>
       <c r="D4" t="n">
-        <v>59.34664872171968</v>
+        <v>63.63492269386975</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.07231483941155</v>
+        <v>34.97476196379262</v>
       </c>
       <c r="C5" t="n">
-        <v>69.18866945679397</v>
+        <v>55.88598806424969</v>
       </c>
       <c r="D5" t="n">
-        <v>38.41087892865646</v>
+        <v>38.97538385859838</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.8692319333527</v>
+        <v>28.29691407950582</v>
       </c>
       <c r="C6" t="n">
-        <v>64.80516595733197</v>
+        <v>68.870583200618</v>
       </c>
       <c r="D6" t="n">
-        <v>33.08686112852601</v>
+        <v>33.56988099901544</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.5581157220977</v>
+        <v>14.3727863901733</v>
       </c>
       <c r="C7" t="n">
-        <v>39.52516257297658</v>
+        <v>49.0471335564664</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>23.78283813537898</v>
+        <v>26.95388322009618</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.287141072844076</v>
+        <v>7.276843753828473</v>
       </c>
       <c r="C21" t="n">
-        <v>75.6040886307573</v>
+        <v>75.49725394597041</v>
       </c>
       <c r="D21" t="n">
-        <v>6.376248438738567</v>
+        <v>5.457632815371355</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.420809912223387</v>
+        <v>5.570436473896402</v>
       </c>
       <c r="C2" t="n">
-        <v>9.574985359519141</v>
+        <v>7.713591712267189</v>
       </c>
       <c r="D2" t="n">
-        <v>22.4074096017292</v>
+        <v>32.04522681432014</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.9905266803228</v>
+        <v>21.73589417202438</v>
       </c>
       <c r="C3" t="n">
-        <v>27.67546778271759</v>
+        <v>18.17215000560846</v>
       </c>
       <c r="D3" t="n">
-        <v>63.57798132702344</v>
+        <v>88.68617886313562</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.62525978108076</v>
+        <v>37.93080430127976</v>
       </c>
       <c r="C4" t="n">
-        <v>64.20924510085413</v>
+        <v>38.4285503873329</v>
       </c>
       <c r="D4" t="n">
-        <v>73.94720057927826</v>
+        <v>86.48019177169304</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.50905369908114</v>
+        <v>43.34416114249668</v>
       </c>
       <c r="C5" t="n">
-        <v>79.84063204787186</v>
+        <v>59.07666810305183</v>
       </c>
       <c r="D5" t="n">
-        <v>51.76264770641309</v>
+        <v>52.62167694762905</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.25415914887547</v>
+        <v>38.7220929509027</v>
       </c>
       <c r="C6" t="n">
-        <v>90.2039608139012</v>
+        <v>79.41651703963724</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>38.60133798328035</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.84054026575129</v>
+        <v>25.03260296288517</v>
       </c>
       <c r="C7" t="n">
-        <v>69.58824077242241</v>
+        <v>77.25372684718151</v>
       </c>
       <c r="D7" t="n">
-        <v>35.33309987584271</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>11.34900346109313</v>
       </c>
       <c r="C8" t="n">
-        <v>39.47116644924301</v>
+        <v>47.98291904506285</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>27.29062268265283</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.499551895788414</v>
+        <v>7.48683140400298</v>
       </c>
       <c r="C21" t="n">
-        <v>85.3074028145932</v>
+        <v>84.22685329503352</v>
       </c>
       <c r="D21" t="n">
-        <v>7.499551895788414</v>
+        <v>6.550977478502607</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_99_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_99_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631153283</v>
+        <v>10.84497630328615</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907186984276</v>
+        <v>37.78907184110739</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.280240064066846</v>
+        <v>7.748934629620075</v>
       </c>
       <c r="C2" t="n">
-        <v>7.982590583230815</v>
+        <v>9.248063374004953</v>
       </c>
       <c r="D2" t="n">
-        <v>31.07722357793278</v>
+        <v>31.69866987472101</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.24854640009046</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="C3" t="n">
-        <v>24.81858196335937</v>
+        <v>26.41392198276044</v>
       </c>
       <c r="D3" t="n">
-        <v>93.31511928865933</v>
+        <v>67.1613604475243</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.24085664937251</v>
+        <v>38.49236398810894</v>
       </c>
       <c r="C4" t="n">
-        <v>42.28289187420587</v>
+        <v>62.53732876052182</v>
       </c>
       <c r="D4" t="n">
-        <v>110.1295122192945</v>
+        <v>85.38259783834509</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.16730768701202</v>
+        <v>46.38757902566179</v>
       </c>
       <c r="C5" t="n">
-        <v>64.81989217289566</v>
+        <v>123.3811427312179</v>
       </c>
       <c r="D5" t="n">
-        <v>70.66129101316419</v>
+        <v>61.26105674500098</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.34853010167018</v>
+        <v>44.39757642915352</v>
       </c>
       <c r="C6" t="n">
-        <v>87.26558993509049</v>
+        <v>140.1965174095573</v>
       </c>
       <c r="D6" t="n">
-        <v>45.44411948188061</v>
+        <v>43.06927178530758</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.69241953559704</v>
+        <v>30.24273802932299</v>
       </c>
       <c r="C7" t="n">
-        <v>97.25585457350601</v>
+        <v>118.9946939886431</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.3600647277471</v>
+        <v>15.60487975900305</v>
       </c>
       <c r="C8" t="n">
-        <v>75.52094214918588</v>
+        <v>82.36372364778616</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>45.15155866601504</v>
+        <v>47.8140584399324</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.683820798839431</v>
+        <v>7.674803653122039</v>
       </c>
       <c r="C21" t="n">
-        <v>93.1663271859281</v>
+        <v>93.05699429410473</v>
       </c>
       <c r="D21" t="n">
-        <v>7.683820798839431</v>
+        <v>8.634154109762294</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.463646958311752</v>
+        <v>7.047966768787852</v>
       </c>
       <c r="C2" t="n">
-        <v>10.29067943591507</v>
+        <v>8.100400307740433</v>
       </c>
       <c r="D2" t="n">
-        <v>32.20917868092936</v>
+        <v>34.38669508894878</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.55288818840697</v>
+        <v>22.25131171675396</v>
       </c>
       <c r="C3" t="n">
-        <v>28.19579406596839</v>
+        <v>31.05758862384785</v>
       </c>
       <c r="D3" t="n">
-        <v>95.48478171504479</v>
+        <v>75.06442946671113</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.06668639509333</v>
+        <v>37.24161741289851</v>
       </c>
       <c r="C4" t="n">
-        <v>51.66349118828415</v>
+        <v>64.11990605976767</v>
       </c>
       <c r="D4" t="n">
-        <v>127.3464217086708</v>
+        <v>97.3412666237755</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.29693944170161</v>
+        <v>51.14905539125883</v>
       </c>
       <c r="C5" t="n">
-        <v>71.22579594310611</v>
+        <v>118.202423591316</v>
       </c>
       <c r="D5" t="n">
-        <v>91.52342972840891</v>
+        <v>74.6128255227576</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.88188114698346</v>
+        <v>52.5284109157256</v>
       </c>
       <c r="C6" t="n">
-        <v>94.10837143369076</v>
+        <v>164.9110341162665</v>
       </c>
       <c r="D6" t="n">
-        <v>55.18502020341747</v>
+        <v>51.2806095836279</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.53189593818607</v>
+        <v>40.42346172236242</v>
       </c>
       <c r="C7" t="n">
-        <v>111.8681874035155</v>
+        <v>158.4000833417016</v>
       </c>
       <c r="D7" t="n">
-        <v>42.63926629084747</v>
+        <v>41.3816474817073</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.62285431731576</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="C8" t="n">
-        <v>100.5555086074795</v>
+        <v>116.6610796956485</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.64531134132641</v>
+        <v>11.31562403914873</v>
       </c>
       <c r="C9" t="n">
-        <v>68.33749419721195</v>
+        <v>73.1078062921472</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>41.85190463204153</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
         <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.866467941310658</v>
+        <v>7.850873913877457</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2807747443747</v>
+        <v>101.0800016411723</v>
       </c>
       <c r="D21" t="n">
-        <v>8.84977643397449</v>
+        <v>9.813592392346822</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.567131377885167</v>
+        <v>7.699847244407733</v>
       </c>
       <c r="C2" t="n">
-        <v>8.52255182056656</v>
+        <v>8.062112147274807</v>
       </c>
       <c r="D2" t="n">
-        <v>27.76284332839555</v>
+        <v>43.17137354654924</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.88101290580366</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="C3" t="n">
-        <v>33.55122779263475</v>
+        <v>30.9495963763807</v>
       </c>
       <c r="D3" t="n">
-        <v>97.61026549473912</v>
+        <v>81.88266727270522</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.7220929509027</v>
+        <v>38.54341486872977</v>
       </c>
       <c r="C4" t="n">
-        <v>59.64019128528948</v>
+        <v>69.18670596138547</v>
       </c>
       <c r="D4" t="n">
-        <v>142.0363126073158</v>
+        <v>107.5259173076319</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.3768619163731</v>
+        <v>52.67076433284139</v>
       </c>
       <c r="C5" t="n">
-        <v>81.877758534184</v>
+        <v>116.7052583423396</v>
       </c>
       <c r="D5" t="n">
-        <v>109.9311991830366</v>
+        <v>88.55364292306231</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.92592092495433</v>
+        <v>59.61270234957058</v>
       </c>
       <c r="C6" t="n">
-        <v>101.6756827380252</v>
+        <v>175.0947030524187</v>
       </c>
       <c r="D6" t="n">
-        <v>68.10580173900973</v>
+        <v>59.65295400544471</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56.17364014159399</v>
+        <v>49.22679338634357</v>
       </c>
       <c r="C7" t="n">
-        <v>122.2884575363912</v>
+        <v>190.8586259395097</v>
       </c>
       <c r="D7" t="n">
-        <v>47.19064864773568</v>
+        <v>45.6934833987593</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>38.30288668118931</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="C8" t="n">
-        <v>122.669375645639</v>
+        <v>155.2143120414207</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>39.63806355896497</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.85781081380023</v>
+        <v>16.19687362466387</v>
       </c>
       <c r="C9" t="n">
-        <v>92.52186714362787</v>
+        <v>103.5046787110369</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>58.36490101747288</v>
+        <v>60.64255569132548</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
         <v>39.98167525545134</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.034155161559148</v>
+        <v>8.010612679913782</v>
       </c>
       <c r="C21" t="n">
-        <v>109.4653640762434</v>
+        <v>109.1445977638253</v>
       </c>
       <c r="D21" t="n">
-        <v>10.04269395194894</v>
+        <v>11.01459243488145</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.682576696358792</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C2" t="n">
-        <v>5.726534358871645</v>
+        <v>5.545892781290231</v>
       </c>
       <c r="D2" t="n">
-        <v>22.95915181151591</v>
+        <v>35.32230065109599</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.94544840138546</v>
+        <v>26.73298998664065</v>
       </c>
       <c r="C3" t="n">
-        <v>46.9079053089126</v>
+        <v>45.46473618366979</v>
       </c>
       <c r="D3" t="n">
-        <v>106.2152841224624</v>
+        <v>87.38045441648735</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.08249216935251</v>
+        <v>25.29571134762332</v>
       </c>
       <c r="C4" t="n">
-        <v>74.07482778083033</v>
+        <v>95.45238404080463</v>
       </c>
       <c r="D4" t="n">
-        <v>133.0385948978938</v>
+        <v>102.0124222005818</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.57010198319369</v>
+        <v>33.57577148524092</v>
       </c>
       <c r="C5" t="n">
-        <v>60.74563920027141</v>
+        <v>104.6297615801038</v>
       </c>
       <c r="D5" t="n">
-        <v>71.29942702092461</v>
+        <v>59.44482349214438</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.85793398698726</v>
+        <v>30.5510068084565</v>
       </c>
       <c r="C6" t="n">
-        <v>80.54356340411259</v>
+        <v>125.7059212948744</v>
       </c>
       <c r="D6" t="n">
-        <v>31.07427833482005</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.3919226226395</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="C7" t="n">
-        <v>86.23671834103982</v>
+        <v>109.113403345399</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>27.84727363096077</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>68.17746932141974</v>
+        <v>76.2719791429347</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>44.48593372253571</v>
+        <v>46.26093357181394</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
         <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1971,7 +1971,7 @@
         <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.138467484027806</v>
+        <v>4.353069320630357</v>
       </c>
       <c r="C2" t="n">
-        <v>2.855904071653971</v>
+        <v>3.07483380970101</v>
       </c>
       <c r="D2" t="n">
-        <v>15.90823979961531</v>
+        <v>25.20048182031137</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.71259426902972</v>
+        <v>26.48755306057895</v>
       </c>
       <c r="C3" t="n">
-        <v>34.87658719336794</v>
+        <v>34.00774047510951</v>
       </c>
       <c r="D3" t="n">
-        <v>101.2623669545373</v>
+        <v>95.31788460532283</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.96458463385165</v>
+        <v>36.50137964389641</v>
       </c>
       <c r="C4" t="n">
-        <v>97.90282631060468</v>
+        <v>107.6152563487184</v>
       </c>
       <c r="D4" t="n">
-        <v>153.5227607470035</v>
+        <v>117.9147715139716</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.12893741108838</v>
+        <v>36.91371367968008</v>
       </c>
       <c r="C5" t="n">
-        <v>96.11310024576277</v>
+        <v>139.2854555400162</v>
       </c>
       <c r="D5" t="n">
-        <v>93.5114688295087</v>
+        <v>75.84001015306612</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.70071548558752</v>
+        <v>36.38749691020379</v>
       </c>
       <c r="C6" t="n">
-        <v>91.25050386662829</v>
+        <v>147.5625704345211</v>
       </c>
       <c r="D6" t="n">
-        <v>39.84913931537804</v>
+        <v>37.31328499530853</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.83487076370406</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>103.0049691295753</v>
+        <v>139.2962547647629</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>30.18285141936394</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>86.45270283597411</v>
+        <v>99.05343461998193</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>27.70492021384499</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>50.69843319500952</v>
+        <v>51.58593311964863</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
         <v>29.89421759431538</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2268,7 +2268,7 @@
         <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.158503348740242</v>
+        <v>3.957424995818893</v>
       </c>
       <c r="C2" t="n">
-        <v>9.371763584740052</v>
+        <v>4.435536127787089</v>
       </c>
       <c r="D2" t="n">
-        <v>15.38791351636451</v>
+        <v>23.77105716292802</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.51776625523235</v>
+        <v>20.62651926622549</v>
       </c>
       <c r="C3" t="n">
-        <v>22.12368451520187</v>
+        <v>22.59492341324034</v>
       </c>
       <c r="D3" t="n">
-        <v>92.13702204356315</v>
+        <v>93.08440857816133</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.88572602234242</v>
+        <v>43.32943492693298</v>
       </c>
       <c r="C4" t="n">
-        <v>92.24894128184729</v>
+        <v>96.15433364934111</v>
       </c>
       <c r="D4" t="n">
-        <v>165.2899887301057</v>
+        <v>135.5273253281594</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.62105505282329</v>
+        <v>44.89041377668541</v>
       </c>
       <c r="C5" t="n">
-        <v>139.2609118474101</v>
+        <v>167.5597894223244</v>
       </c>
       <c r="D5" t="n">
-        <v>123.5774922720673</v>
+        <v>96.70214886831084</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.69821221083129</v>
+        <v>42.42524529132167</v>
       </c>
       <c r="C6" t="n">
-        <v>120.2719477518683</v>
+        <v>183.2657891948649</v>
       </c>
       <c r="D6" t="n">
-        <v>56.714583126634</v>
+        <v>49.34853010167018</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.55457394637499</v>
+        <v>28.98511922018283</v>
       </c>
       <c r="C7" t="n">
-        <v>118.3958278890526</v>
+        <v>173.0124161717111</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.68971097219578</v>
+        <v>13.51866588747858</v>
       </c>
       <c r="C8" t="n">
-        <v>110.736232300519</v>
+        <v>138.1073582949201</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.2069942013426</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>75.65936857548466</v>
+        <v>82.31561801027804</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>44.55661955724149</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.621667280966483</v>
+        <v>2.402336632291945</v>
       </c>
       <c r="C2" t="n">
-        <v>4.319689898685966</v>
+        <v>2.131374265919825</v>
       </c>
       <c r="D2" t="n">
-        <v>10.64018161862693</v>
+        <v>16.59055445406685</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.61732368398877</v>
+        <v>19.71840263979719</v>
       </c>
       <c r="C3" t="n">
-        <v>29.92367002544278</v>
+        <v>21.80461651132166</v>
       </c>
       <c r="D3" t="n">
-        <v>88.21984870361838</v>
+        <v>93.67836593923064</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.76108512163209</v>
+        <v>47.37521721613408</v>
       </c>
       <c r="C4" t="n">
-        <v>87.51397210426492</v>
+        <v>91.53422895315562</v>
       </c>
       <c r="D4" t="n">
-        <v>175.9340973395497</v>
+        <v>147.5880958748315</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.70726892434777</v>
+        <v>46.38757902566179</v>
       </c>
       <c r="C5" t="n">
-        <v>168.4188186635403</v>
+        <v>196.6440651606362</v>
       </c>
       <c r="D5" t="n">
-        <v>133.3704256219292</v>
+        <v>102.641722479004</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.25794727097221</v>
+        <v>34.81768233111314</v>
       </c>
       <c r="C6" t="n">
-        <v>150.0581730987165</v>
+        <v>219.6130344491945</v>
       </c>
       <c r="D6" t="n">
-        <v>54.98376192404687</v>
+        <v>48.50324532831367</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.0191362324662</v>
+        <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>131.810428519881</v>
+        <v>180.6180156365112</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>90.45823346930109</v>
+        <v>102.558273924143</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.173409490753191</v>
+        <v>3.860231973098458</v>
       </c>
       <c r="C2" t="n">
-        <v>8.329147522829938</v>
+        <v>6.899722865446583</v>
       </c>
       <c r="D2" t="n">
-        <v>13.54320958008475</v>
+        <v>13.74152261634261</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6679325962531</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C3" t="n">
-        <v>23.17415455874596</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="D3" t="n">
-        <v>77.52861620437062</v>
+        <v>86.82085822506667</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.57865997509143</v>
+        <v>43.26562132615693</v>
       </c>
       <c r="C4" t="n">
-        <v>81.86008707550754</v>
+        <v>74.11311594129596</v>
       </c>
       <c r="D4" t="n">
-        <v>179.3034554605247</v>
+        <v>157.836560159464</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.9791152274329</v>
+        <v>56.72047361285948</v>
       </c>
       <c r="C5" t="n">
-        <v>166.4553232550467</v>
+        <v>185.3294228691917</v>
       </c>
       <c r="D5" t="n">
-        <v>162.0620022785423</v>
+        <v>125.5900750657732</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.00513938936205</v>
+        <v>45.24286120251001</v>
       </c>
       <c r="C6" t="n">
-        <v>203.4318687877986</v>
+        <v>262.2395380198868</v>
       </c>
       <c r="D6" t="n">
-        <v>76.23663622558183</v>
+        <v>63.95988118397546</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.77498415374501</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>169.7785392339221</v>
+        <v>241.3430381349934</v>
       </c>
       <c r="D7" t="n">
-        <v>41.02232782195297</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>127.7597374921587</v>
+        <v>157.1336288032232</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>32.71183350550372</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>63.23436963053704</v>
+        <v>67.00624431025328</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3131,7 +3131,7 @@
         <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.133738671955819</v>
+        <v>2.66249977391735</v>
       </c>
       <c r="C2" t="n">
-        <v>4.595561003579319</v>
+        <v>4.733005682173872</v>
       </c>
       <c r="D2" t="n">
-        <v>10.0187353218387</v>
+        <v>10.01775357413445</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.97932654494859</v>
+        <v>13.86227758396496</v>
       </c>
       <c r="C3" t="n">
-        <v>27.67055904419635</v>
+        <v>20.45962215650353</v>
       </c>
       <c r="D3" t="n">
-        <v>72.12900383101315</v>
+        <v>80.75365741282138</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.99684343937156</v>
+        <v>38.17329598422873</v>
       </c>
       <c r="C4" t="n">
-        <v>73.5898444149324</v>
+        <v>60.48253081553325</v>
       </c>
       <c r="D4" t="n">
-        <v>178.5632176915226</v>
+        <v>163.0182245424786</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.67954330891737</v>
+        <v>61.70284321191205</v>
       </c>
       <c r="C5" t="n">
-        <v>166.0871678659542</v>
+        <v>173.3766445699867</v>
       </c>
       <c r="D5" t="n">
-        <v>181.2797135891736</v>
+        <v>141.7643684932394</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.98125864929064</v>
+        <v>53.05168244208915</v>
       </c>
       <c r="C6" t="n">
-        <v>233.3791007581433</v>
+        <v>285.7465050503724</v>
       </c>
       <c r="D6" t="n">
-        <v>93.18258334858602</v>
+        <v>77.32343093418305</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.33770551472768</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>212.2381456948924</v>
+        <v>292.785636089822</v>
       </c>
       <c r="D7" t="n">
-        <v>46.8912155979404</v>
+        <v>42.57937968088841</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>160.2212253330794</v>
+        <v>199.6923917823225</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>72.88593131098743</v>
+        <v>75.88124355664445</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.923464736797754</v>
+        <v>4.948990177108171</v>
       </c>
       <c r="C2" t="n">
-        <v>4.689808783187013</v>
+        <v>5.450663253978291</v>
       </c>
       <c r="D2" t="n">
-        <v>23.5776528651914</v>
+        <v>12.46328710541326</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.89173001509237</v>
+        <v>11.50608309377262</v>
       </c>
       <c r="C3" t="n">
-        <v>22.87963024747192</v>
+        <v>19.32570355809846</v>
       </c>
       <c r="D3" t="n">
-        <v>64.86407081958676</v>
+        <v>71.9032018590364</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.39851711912875</v>
+        <v>32.53217367562655</v>
       </c>
       <c r="C4" t="n">
-        <v>71.34360566761571</v>
+        <v>56.14320596276234</v>
       </c>
       <c r="D4" t="n">
-        <v>174.4153336410799</v>
+        <v>164.817768084363</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.38501899764334</v>
+        <v>59.96024103687396</v>
       </c>
       <c r="C5" t="n">
-        <v>152.4899621621358</v>
+        <v>146.746738092292</v>
       </c>
       <c r="D5" t="n">
-        <v>195.8095796120264</v>
+        <v>160.5157496443535</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73.78128521726055</v>
+        <v>64.24164277509429</v>
       </c>
       <c r="C6" t="n">
-        <v>246.7023988524768</v>
+        <v>282.7678825156876</v>
       </c>
       <c r="D6" t="n">
-        <v>119.3864113226376</v>
+        <v>95.67818601278141</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.58504918293564</v>
+        <v>32.5184292077671</v>
       </c>
       <c r="C7" t="n">
-        <v>265.776774998288</v>
+        <v>344.7672135342821</v>
       </c>
       <c r="D7" t="n">
-        <v>58.09001166028376</v>
+        <v>50.66407202536089</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.51590057081509</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>207.9537987135594</v>
+        <v>271.0409061884594</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>120.2562397886003</v>
+        <v>137.8953007908027</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3697,7 +3697,7 @@
         <v>51.81664383014665</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
         <v>20.39482680802324</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.61189086165302</v>
+        <v>5.992587986722531</v>
       </c>
       <c r="C2" t="n">
-        <v>8.884816723433634</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="D2" t="n">
-        <v>5.820782138479339</v>
+        <v>5.668611244321084</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.523492510541802</v>
+        <v>3.575525138866883</v>
       </c>
       <c r="C2" t="n">
-        <v>2.663481521621597</v>
+        <v>3.139629158181299</v>
       </c>
       <c r="D2" t="n">
-        <v>17.35337242026662</v>
+        <v>9.172468800777949</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.77592484372025</v>
+        <v>15.83068173097982</v>
       </c>
       <c r="C3" t="n">
-        <v>24.98547907308132</v>
+        <v>22.80109043113217</v>
       </c>
       <c r="D3" t="n">
-        <v>74.31830121148354</v>
+        <v>77.27336180126645</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.47579745032376</v>
+        <v>45.40975831223197</v>
       </c>
       <c r="C4" t="n">
-        <v>99.12804744550469</v>
+        <v>82.89386740807944</v>
       </c>
       <c r="D4" t="n">
-        <v>179.1758282589726</v>
+        <v>167.1788713130766</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.4914232981337</v>
+        <v>37.28186906877263</v>
       </c>
       <c r="C5" t="n">
-        <v>217.4571164906685</v>
+        <v>229.5571569455105</v>
       </c>
       <c r="D5" t="n">
-        <v>178.5308200172825</v>
+        <v>144.145106676038</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.55351008321273</v>
+        <v>20.16607959293373</v>
       </c>
       <c r="C6" t="n">
-        <v>223.3966901013617</v>
+        <v>282.4861209245688</v>
       </c>
       <c r="D6" t="n">
-        <v>91.77377539299185</v>
+        <v>75.91462297858888</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.60559946480004</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>146.2431015200134</v>
+        <v>190.6190794996734</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>31.79978988825843</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>88.62236526235957</v>
+        <v>101.6403398206723</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>24.45042657426681</v>
       </c>
     </row>
     <row r="9">
@@ -4305,7 +4305,7 @@
         <v>39.49374664644068</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.34806277111788</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
         <v>16.34806277111788</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.576147033672636</v>
+        <v>7.167739988705962</v>
       </c>
       <c r="C2" t="n">
-        <v>4.498367980858886</v>
+        <v>4.846888415866503</v>
       </c>
       <c r="D2" t="n">
-        <v>15.82773648786708</v>
+        <v>12.15894531709675</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.28014225307561</v>
+        <v>12.7283589855599</v>
       </c>
       <c r="C3" t="n">
-        <v>22.38875639534851</v>
+        <v>26.16848505669873</v>
       </c>
       <c r="D3" t="n">
-        <v>8.025787482217675</v>
+        <v>7.898160280665589</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
         <v>9.35114688295087</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39799892202218</v>
+        <v>13.3982172200532</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14246494470437</v>
+        <v>70.14360779910207</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576235167296727</v>
+        <v>1.576260849418024</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.023603002630929</v>
+        <v>5.137485736323558</v>
       </c>
       <c r="C2" t="n">
-        <v>4.308890673939251</v>
+        <v>4.331470871136927</v>
       </c>
       <c r="D2" t="n">
-        <v>20.14251764803181</v>
+        <v>18.82992096745382</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.08579726536375</v>
+        <v>19.93438713473148</v>
       </c>
       <c r="C3" t="n">
-        <v>19.35515598922587</v>
+        <v>21.622993186036</v>
       </c>
       <c r="D3" t="n">
-        <v>19.37969968183204</v>
+        <v>16.19883712007237</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.0840136964045</v>
+        <v>14.81751810019711</v>
       </c>
       <c r="C4" t="n">
-        <v>34.66354794154638</v>
+        <v>40.41953473154543</v>
       </c>
       <c r="D4" t="n">
-        <v>19.27170743436488</v>
+        <v>19.20789383358884</v>
       </c>
     </row>
     <row r="5">
@@ -4865,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
         <v>5.375068680751288</v>
@@ -4885,7 +4885,7 @@
         <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4396700493378</v>
+        <v>15.44095361390079</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13710659104245</v>
+        <v>86.14426753018336</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250456852492168</v>
+        <v>3.250727076610692</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.101161071266427</v>
+        <v>5.543929285881738</v>
       </c>
       <c r="C2" t="n">
-        <v>2.526036843027043</v>
+        <v>9.255917355638928</v>
       </c>
       <c r="D2" t="n">
-        <v>29.21288468756809</v>
+        <v>24.95504489424967</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.87548227247668</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="C3" t="n">
-        <v>17.78435966243097</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D3" t="n">
-        <v>30.99377502307181</v>
+        <v>27.50366193447439</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.57420890045992</v>
+        <v>28.32047602440774</v>
       </c>
       <c r="C4" t="n">
-        <v>42.80616340056942</v>
+        <v>48.52386203010285</v>
       </c>
       <c r="D4" t="n">
-        <v>24.65757533986289</v>
+        <v>23.01118443984099</v>
       </c>
     </row>
     <row r="5">
@@ -5176,10 +5176,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.7450897542611</v>
+        <v>12.90998231084556</v>
       </c>
       <c r="C5" t="n">
-        <v>38.77903431774902</v>
+        <v>44.84132639147307</v>
       </c>
       <c r="D5" t="n">
         <v>29.59969328304134</v>
@@ -5196,7 +5196,7 @@
         <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73097692048468</v>
+        <v>16.73341752558114</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0589592149565</v>
+        <v>102.0738469060449</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18274423012117</v>
+        <v>5.02002525767434</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.613052535806514</v>
+        <v>5.953318078552658</v>
       </c>
       <c r="C2" t="n">
-        <v>3.98295043612931</v>
+        <v>11.36176618124834</v>
       </c>
       <c r="D2" t="n">
-        <v>36.23630776374977</v>
+        <v>26.42275771209865</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.73174619702914</v>
+        <v>19.03608798534566</v>
       </c>
       <c r="C3" t="n">
-        <v>13.17014545247096</v>
+        <v>28.6424892714007</v>
       </c>
       <c r="D3" t="n">
-        <v>46.29922173227958</v>
+        <v>40.34983064454391</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.45032876327557</v>
+        <v>32.34073287329843</v>
       </c>
       <c r="C4" t="n">
-        <v>43.75060469205486</v>
+        <v>47.60494617892783</v>
       </c>
       <c r="D4" t="n">
-        <v>34.10198825471721</v>
+        <v>31.15379989886403</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.65569395991241</v>
+        <v>27.53802310412304</v>
       </c>
       <c r="C5" t="n">
-        <v>60.52474596681587</v>
+        <v>69.01686360855078</v>
       </c>
       <c r="D5" t="n">
-        <v>31.48955761371645</v>
+        <v>30.92505268377453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.01386764104647</v>
+        <v>11.79373517111693</v>
       </c>
       <c r="C6" t="n">
-        <v>37.59504658642736</v>
+        <v>42.58625191481815</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>37.91705983342032</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05344634205536</v>
+        <v>18.05615626642192</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7772451838849</v>
+        <v>117.7949242142763</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017815447351785</v>
+        <v>6.878535720541682</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.622870012848982</v>
+        <v>6.218389958699297</v>
       </c>
       <c r="C2" t="n">
-        <v>4.746750150033328</v>
+        <v>6.261586857686157</v>
       </c>
       <c r="D2" t="n">
-        <v>34.29539255245383</v>
+        <v>25.03456645829367</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.64338890364693</v>
+        <v>17.62237129123025</v>
       </c>
       <c r="C3" t="n">
-        <v>13.61193191938202</v>
+        <v>35.49508824704343</v>
       </c>
       <c r="D3" t="n">
-        <v>59.77370897306705</v>
+        <v>48.40507055788899</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.48264432205771</v>
+        <v>25.39781310886498</v>
       </c>
       <c r="C4" t="n">
-        <v>31.53668150352029</v>
+        <v>50.48932093400496</v>
       </c>
       <c r="D4" t="n">
-        <v>42.60195987808609</v>
+        <v>38.10948238345269</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.26804248545517</v>
+        <v>23.16924582022473</v>
       </c>
       <c r="C5" t="n">
-        <v>53.06346341454012</v>
+        <v>58.83123117699012</v>
       </c>
       <c r="D5" t="n">
-        <v>29.25608158655496</v>
+        <v>28.10252803406495</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.82519215538184</v>
+        <v>13.32329809433347</v>
       </c>
       <c r="C6" t="n">
-        <v>45.60512610537709</v>
+        <v>51.88438442173969</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>30.51075515258238</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.587527095496098</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>26.70942804173872</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
         <v>33.45305302221006</v>
@@ -5888,7 +5888,7 @@
         <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.054533562540935</v>
+        <v>7.055082647939839</v>
       </c>
       <c r="C21" t="n">
-        <v>66.13625214882126</v>
+        <v>66.14139982443599</v>
       </c>
       <c r="D21" t="n">
-        <v>4.409083476588084</v>
+        <v>5.291311985954879</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.323436963053706</v>
+        <v>6.364670366632072</v>
       </c>
       <c r="C2" t="n">
-        <v>4.899902791895831</v>
+        <v>4.364850293081319</v>
       </c>
       <c r="D2" t="n">
-        <v>39.69205968269854</v>
+        <v>26.62008900065226</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.50518346152638</v>
+        <v>20.14055415262332</v>
       </c>
       <c r="C3" t="n">
-        <v>16.79279448114169</v>
+        <v>28.38232612977529</v>
       </c>
       <c r="D3" t="n">
-        <v>74.13667788619789</v>
+        <v>57.73658248675491</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.94058072059322</v>
+        <v>30.89854549575986</v>
       </c>
       <c r="C4" t="n">
-        <v>33.20859784385261</v>
+        <v>74.71296378859076</v>
       </c>
       <c r="D4" t="n">
-        <v>63.63492269386975</v>
+        <v>54.2670860999467</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.97476196379262</v>
+        <v>32.12769362147687</v>
       </c>
       <c r="C5" t="n">
-        <v>55.88598806424969</v>
+        <v>80.01243789611506</v>
       </c>
       <c r="D5" t="n">
-        <v>38.97538385859838</v>
+        <v>36.34920874973816</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.29691407950582</v>
+        <v>23.58747034223387</v>
       </c>
       <c r="C6" t="n">
-        <v>68.870583200618</v>
+        <v>76.47814616082654</v>
       </c>
       <c r="D6" t="n">
-        <v>33.56988099901544</v>
+        <v>33.04660947265189</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.3727863901733</v>
+        <v>11.61800233205675</v>
       </c>
       <c r="C7" t="n">
-        <v>49.0471335564664</v>
+        <v>54.85613472249477</v>
       </c>
       <c r="D7" t="n">
         <v>32.87774886752143</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>26.95388322009618</v>
+        <v>28.37250865273282</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
         <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6266,7 +6266,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.276843753828473</v>
+        <v>7.275592441106062</v>
       </c>
       <c r="C21" t="n">
-        <v>75.49725394597041</v>
+        <v>75.48427157647541</v>
       </c>
       <c r="D21" t="n">
-        <v>5.457632815371355</v>
+        <v>6.366143385967804</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.570436473896402</v>
+        <v>4.982369599052562</v>
       </c>
       <c r="C2" t="n">
-        <v>7.713591712267189</v>
+        <v>7.820602212030092</v>
       </c>
       <c r="D2" t="n">
-        <v>32.04522681432014</v>
+        <v>21.52089142479433</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.73589417202438</v>
+        <v>21.39719121405923</v>
       </c>
       <c r="C3" t="n">
-        <v>18.17215000560846</v>
+        <v>21.56899706230243</v>
       </c>
       <c r="D3" t="n">
-        <v>88.68617886313562</v>
+        <v>65.63474276742051</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.93080430127976</v>
+        <v>35.36549755008285</v>
       </c>
       <c r="C4" t="n">
-        <v>38.4285503873329</v>
+        <v>72.64540312344698</v>
       </c>
       <c r="D4" t="n">
-        <v>86.48019177169304</v>
+        <v>71.01177494358029</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.34416114249668</v>
+        <v>40.10439371848221</v>
       </c>
       <c r="C5" t="n">
-        <v>59.07666810305183</v>
+        <v>111.7965198211056</v>
       </c>
       <c r="D5" t="n">
-        <v>52.62167694762905</v>
+        <v>47.2956956520901</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.7220929509027</v>
+        <v>34.09315252537899</v>
       </c>
       <c r="C6" t="n">
-        <v>79.41651703963724</v>
+        <v>104.4932986492135</v>
       </c>
       <c r="D6" t="n">
-        <v>38.60133798328035</v>
+        <v>37.39378830705677</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.03260296288517</v>
+        <v>20.48122060599696</v>
       </c>
       <c r="C7" t="n">
-        <v>77.25372684718151</v>
+        <v>85.39830580161305</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>47.98291904506285</v>
+        <v>52.07189823325082</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.48683140400298</v>
+        <v>7.482443661859187</v>
       </c>
       <c r="C21" t="n">
-        <v>84.22685329503352</v>
+        <v>84.17749119591586</v>
       </c>
       <c r="D21" t="n">
-        <v>6.550977478502607</v>
+        <v>7.482443661859187</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_99_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_99_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497630328615</v>
+        <v>10.84497646545653</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907184110739</v>
+        <v>37.78907240618636</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.748934629620075</v>
+        <v>1.022981107825176</v>
       </c>
       <c r="C2" t="n">
-        <v>9.248063374004953</v>
+        <v>2.420989838672635</v>
       </c>
       <c r="D2" t="n">
-        <v>31.69866987472101</v>
+        <v>13.49117695175967</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.99190933865455</v>
+        <v>9.508226515630358</v>
       </c>
       <c r="C3" t="n">
-        <v>26.41392198276044</v>
+        <v>36.70263792326701</v>
       </c>
       <c r="D3" t="n">
-        <v>67.1613604475243</v>
+        <v>58.89013603924492</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.49236398810894</v>
+        <v>17.61255381418778</v>
       </c>
       <c r="C4" t="n">
-        <v>62.53732876052182</v>
+        <v>141.0152949948991</v>
       </c>
       <c r="D4" t="n">
-        <v>85.38259783834509</v>
+        <v>58.33839382945821</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.38757902566179</v>
+        <v>16.88606051304514</v>
       </c>
       <c r="C5" t="n">
-        <v>123.3811427312179</v>
+        <v>182.1387428303895</v>
       </c>
       <c r="D5" t="n">
-        <v>61.26105674500098</v>
+        <v>38.85266539556753</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.39757642915352</v>
+        <v>10.86794708601219</v>
       </c>
       <c r="C6" t="n">
-        <v>140.1965174095573</v>
+        <v>131.4619080848734</v>
       </c>
       <c r="D6" t="n">
-        <v>43.06927178530758</v>
+        <v>28.53842401475054</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.24273802932299</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>118.9946939886431</v>
+        <v>65.0368584155342</v>
       </c>
       <c r="D7" t="n">
-        <v>38.38731698375453</v>
+        <v>29.22466566001905</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.60487975900305</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>82.36372364778616</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>47.8140584399324</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.64235040268046</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.674803653122039</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.05699429410473</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.634154109762294</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.047966768787852</v>
+        <v>0.7844164156932014</v>
       </c>
       <c r="C2" t="n">
-        <v>8.100400307740433</v>
+        <v>5.316163818496478</v>
       </c>
       <c r="D2" t="n">
-        <v>34.38669508894878</v>
+        <v>14.61625982082651</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.25131171675396</v>
+        <v>6.376451339083033</v>
       </c>
       <c r="C3" t="n">
-        <v>31.05758862384785</v>
+        <v>21.52972715413255</v>
       </c>
       <c r="D3" t="n">
-        <v>75.06442946671113</v>
+        <v>56.60757262687108</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.24161741289851</v>
+        <v>18.11029990024091</v>
       </c>
       <c r="C4" t="n">
-        <v>64.11990605976767</v>
+        <v>114.4433116317549</v>
       </c>
       <c r="D4" t="n">
-        <v>97.3412666237755</v>
+        <v>72.93894568701677</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.14905539125883</v>
+        <v>21.50027472300515</v>
       </c>
       <c r="C5" t="n">
-        <v>118.202423591316</v>
+        <v>224.5256999612456</v>
       </c>
       <c r="D5" t="n">
-        <v>74.6128255227576</v>
+        <v>49.62734644967627</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.5284109157256</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="C6" t="n">
-        <v>164.9110341162665</v>
+        <v>210.0733920070283</v>
       </c>
       <c r="D6" t="n">
-        <v>51.2806095836279</v>
+        <v>33.52962934314132</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.42346172236242</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
-        <v>158.4000833417016</v>
+        <v>124.4443754949172</v>
       </c>
       <c r="D7" t="n">
-        <v>41.3816474817073</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.53249247079604</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>116.6610796956485</v>
+        <v>56.74501730546564</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.31562403914873</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>73.1078062921472</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>43.2754388031994</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>38.72012945549421</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
         <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.84931924182727</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>44.53403936004381</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.850873913877457</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0800016411723</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.813592392346822</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.699847244407733</v>
+        <v>0.4319689898685966</v>
       </c>
       <c r="C2" t="n">
-        <v>8.062112147274807</v>
+        <v>2.410190613925919</v>
       </c>
       <c r="D2" t="n">
-        <v>43.17137354654924</v>
+        <v>10.09040290424872</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.37403017978481</v>
+        <v>5.566509483079415</v>
       </c>
       <c r="C3" t="n">
-        <v>30.9495963763807</v>
+        <v>22.59001467471911</v>
       </c>
       <c r="D3" t="n">
-        <v>81.88266727270522</v>
+        <v>57.09353774047326</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.54341486872977</v>
+        <v>19.53972455762427</v>
       </c>
       <c r="C4" t="n">
-        <v>69.18670596138547</v>
+        <v>102.2804393238412</v>
       </c>
       <c r="D4" t="n">
-        <v>107.5259173076319</v>
+        <v>81.3495782692992</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.67076433284139</v>
+        <v>21.25483779694345</v>
       </c>
       <c r="C5" t="n">
-        <v>116.7052583423396</v>
+        <v>254.8862477150782</v>
       </c>
       <c r="D5" t="n">
-        <v>88.55364292306231</v>
+        <v>55.02695882303374</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.61270234957058</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>175.0947030524187</v>
+        <v>252.5388889542241</v>
       </c>
       <c r="D6" t="n">
-        <v>59.65295400544471</v>
+        <v>34.41516577237194</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.22679338634357</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>190.8586259395097</v>
+        <v>112.0478472333927</v>
       </c>
       <c r="D7" t="n">
-        <v>45.6934833987593</v>
+        <v>32.39865598784899</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.62700229231099</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>155.2143120414207</v>
+        <v>44.2277340763188</v>
       </c>
       <c r="D8" t="n">
-        <v>39.63806355896497</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.19687362466387</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>103.5046787110369</v>
+        <v>25.4046853427947</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>40.38124657107979</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>60.64255569132548</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.98167525545134</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>38.52377991464484</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.010612679913782</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.1445977638253</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.01459243488145</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.159886007071988</v>
+        <v>0.6047565858160352</v>
       </c>
       <c r="C2" t="n">
-        <v>5.545892781290231</v>
+        <v>13.25653925044468</v>
       </c>
       <c r="D2" t="n">
-        <v>35.32230065109599</v>
+        <v>11.0652783745658</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.73298998664065</v>
+        <v>3.539200473809752</v>
       </c>
       <c r="C3" t="n">
-        <v>45.46473618366979</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D3" t="n">
-        <v>87.38045441648735</v>
+        <v>52.75421288770235</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.29571134762332</v>
+        <v>15.36631506687108</v>
       </c>
       <c r="C4" t="n">
-        <v>95.45238404080463</v>
+        <v>79.38411936539708</v>
       </c>
       <c r="D4" t="n">
-        <v>102.0124222005818</v>
+        <v>89.82402445235768</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.57577148524092</v>
+        <v>25.10819753611218</v>
       </c>
       <c r="C5" t="n">
-        <v>104.6297615801038</v>
+        <v>224.6484184242764</v>
       </c>
       <c r="D5" t="n">
-        <v>59.44482349214438</v>
+        <v>68.9186888381261</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.5510068084565</v>
+        <v>19.0390332284584</v>
       </c>
       <c r="C6" t="n">
-        <v>125.7059212948744</v>
+        <v>325.6358960216246</v>
       </c>
       <c r="D6" t="n">
-        <v>30.06798693796707</v>
+        <v>41.98247707670636</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.9603134856694</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>109.113403345399</v>
+        <v>225.2934266659665</v>
       </c>
       <c r="D7" t="n">
-        <v>27.84727363096077</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>76.2719791429347</v>
+        <v>88.20512248805467</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>46.26093357181394</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.60245859970483</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>25.58827216348886</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>45.80540263704344</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.353069320630357</v>
+        <v>0.3593196597543326</v>
       </c>
       <c r="C2" t="n">
-        <v>3.07483380970101</v>
+        <v>6.860452957276711</v>
       </c>
       <c r="D2" t="n">
-        <v>25.20048182031137</v>
+        <v>8.448920742748049</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.48755306057895</v>
+        <v>2.945243112740431</v>
       </c>
       <c r="C3" t="n">
-        <v>34.00774047510951</v>
+        <v>33.11435006424491</v>
       </c>
       <c r="D3" t="n">
-        <v>95.31788460532283</v>
+        <v>50.12803777884214</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.50137964389641</v>
+        <v>12.31602494977624</v>
       </c>
       <c r="C4" t="n">
-        <v>107.6152563487184</v>
+        <v>63.14993932797183</v>
       </c>
       <c r="D4" t="n">
-        <v>117.9147715139716</v>
+        <v>95.63106212297755</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.91371367968008</v>
+        <v>25.99177046993431</v>
       </c>
       <c r="C5" t="n">
-        <v>139.2854555400162</v>
+        <v>200.939211366716</v>
       </c>
       <c r="D5" t="n">
-        <v>75.84001015306612</v>
+        <v>79.42338927356697</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.38749691020379</v>
+        <v>23.2252054393668</v>
       </c>
       <c r="C6" t="n">
-        <v>147.5625704345211</v>
+        <v>353.2082802953963</v>
       </c>
       <c r="D6" t="n">
-        <v>37.31328499530853</v>
+        <v>49.50953672516665</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>139.2962547647629</v>
+        <v>309.1945672186032</v>
       </c>
       <c r="D7" t="n">
-        <v>30.18285141936394</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>99.05343461998193</v>
+        <v>137.4397698560322</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>51.58593311964863</v>
+        <v>46.59374604355361</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.74128593663113</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.51842920776709</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>39.26499943135118</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.957424995818893</v>
+        <v>0.3603014074585794</v>
       </c>
       <c r="C2" t="n">
-        <v>4.435536127787089</v>
+        <v>8.526478811383548</v>
       </c>
       <c r="D2" t="n">
-        <v>23.77105716292802</v>
+        <v>12.9443434804942</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.62651926622549</v>
+        <v>2.115666302651876</v>
       </c>
       <c r="C3" t="n">
-        <v>22.59492341324034</v>
+        <v>29.74204670015712</v>
       </c>
       <c r="D3" t="n">
-        <v>93.08440857816133</v>
+        <v>45.82798283424111</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.32943492693298</v>
+        <v>9.189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>96.15433364934111</v>
+        <v>72.18594519785947</v>
       </c>
       <c r="D4" t="n">
-        <v>135.5273253281594</v>
+        <v>98.04321623231196</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.89041377668541</v>
+        <v>23.34105166846792</v>
       </c>
       <c r="C5" t="n">
-        <v>167.5597894223244</v>
+        <v>164.3445656909161</v>
       </c>
       <c r="D5" t="n">
-        <v>96.70214886831084</v>
+        <v>92.03884727313849</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.42524529132167</v>
+        <v>28.01515248838698</v>
       </c>
       <c r="C6" t="n">
-        <v>183.2657891948649</v>
+        <v>340.5290086950487</v>
       </c>
       <c r="D6" t="n">
-        <v>49.34853010167018</v>
+        <v>59.69320566131882</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.98511922018283</v>
+        <v>15.03153909972291</v>
       </c>
       <c r="C7" t="n">
-        <v>173.0124161717111</v>
+        <v>393.8143470907485</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>41.86074036137975</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.51866588747858</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>138.1073582949201</v>
+        <v>247.9256564919682</v>
       </c>
       <c r="D8" t="n">
-        <v>29.2069942013426</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>82.31561801027804</v>
+        <v>93.63124204942677</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>41.3796839862988</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>44.55661955724149</v>
+        <v>40.42837046088366</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>38.43836786437537</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.402336632291945</v>
+        <v>0.2503456645829367</v>
       </c>
       <c r="C2" t="n">
-        <v>2.131374265919825</v>
+        <v>4.707480241863456</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59055445406685</v>
+        <v>9.527861469715294</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.71840263979719</v>
+        <v>3.072870314292516</v>
       </c>
       <c r="C3" t="n">
-        <v>21.80461651132166</v>
+        <v>35.41163969218245</v>
       </c>
       <c r="D3" t="n">
-        <v>93.67836593923064</v>
+        <v>50.30475236560656</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.37521721613408</v>
+        <v>15.77472211183775</v>
       </c>
       <c r="C4" t="n">
-        <v>91.53422895315562</v>
+        <v>104.3735254292954</v>
       </c>
       <c r="D4" t="n">
-        <v>147.5880958748315</v>
+        <v>99.49816633000574</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.38757902566179</v>
+        <v>16.64062358698344</v>
       </c>
       <c r="C5" t="n">
-        <v>196.6440651606362</v>
+        <v>267.5753367924682</v>
       </c>
       <c r="D5" t="n">
-        <v>102.641722479004</v>
+        <v>84.97026380256145</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.81768233111314</v>
+        <v>9.298132506921544</v>
       </c>
       <c r="C6" t="n">
-        <v>219.6130344491945</v>
+        <v>332.8006907672178</v>
       </c>
       <c r="D6" t="n">
-        <v>48.50324532831367</v>
+        <v>52.93092747446678</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.92310488389926</v>
+        <v>3.712969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>180.6180156365112</v>
+        <v>174.3299215908104</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>102.558273924143</v>
+        <v>69.01195487002953</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.40312275801371</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>23.63066724122073</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.860231973098458</v>
+        <v>0.1629701189049705</v>
       </c>
       <c r="C2" t="n">
-        <v>6.899722865446583</v>
+        <v>2.174571164906685</v>
       </c>
       <c r="D2" t="n">
-        <v>13.74152261634261</v>
+        <v>6.846708489417256</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.18625432636641</v>
+        <v>1.983130362578557</v>
       </c>
       <c r="C3" t="n">
-        <v>14.93729132011522</v>
+        <v>26.48755306057895</v>
       </c>
       <c r="D3" t="n">
-        <v>86.82085822506667</v>
+        <v>46.40721397974673</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.26562132615693</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C4" t="n">
-        <v>74.11311594129596</v>
+        <v>92.31275488262334</v>
       </c>
       <c r="D4" t="n">
-        <v>157.836560159464</v>
+        <v>97.30297846330987</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.72047361285948</v>
+        <v>15.48707003449344</v>
       </c>
       <c r="C5" t="n">
-        <v>185.3294228691917</v>
+        <v>210.3639893274853</v>
       </c>
       <c r="D5" t="n">
-        <v>125.5900750657732</v>
+        <v>88.65181769348699</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.24286120251001</v>
+        <v>9.177377539299185</v>
       </c>
       <c r="C6" t="n">
-        <v>262.2395380198868</v>
+        <v>311.6283197774311</v>
       </c>
       <c r="D6" t="n">
-        <v>63.95988118397546</v>
+        <v>55.34602682691394</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.40326162673396</v>
+        <v>3.054217107911827</v>
       </c>
       <c r="C7" t="n">
-        <v>241.3430381349934</v>
+        <v>217.2686209314531</v>
       </c>
       <c r="D7" t="n">
-        <v>38.38731698375453</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>157.1336288032232</v>
+        <v>82.69751786723006</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>26.36974333606933</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>67.00624431025328</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>16.51299638543135</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.458296251434013</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.66249977391735</v>
+        <v>0.4751658888554562</v>
       </c>
       <c r="C2" t="n">
-        <v>4.733005682173872</v>
+        <v>16.21258158793183</v>
       </c>
       <c r="D2" t="n">
-        <v>10.01775357413445</v>
+        <v>9.519025740377073</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.86227758396496</v>
+        <v>1.207549676223577</v>
       </c>
       <c r="C3" t="n">
-        <v>20.45962215650353</v>
+        <v>16.05648370295658</v>
       </c>
       <c r="D3" t="n">
-        <v>80.75365741282138</v>
+        <v>41.28739970209961</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.17329598422873</v>
+        <v>7.096072406295946</v>
       </c>
       <c r="C4" t="n">
-        <v>60.48253081553325</v>
+        <v>78.66940703670541</v>
       </c>
       <c r="D4" t="n">
-        <v>163.0182245424786</v>
+        <v>98.60477591914113</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.70284321191205</v>
+        <v>15.95340019401067</v>
       </c>
       <c r="C5" t="n">
-        <v>173.3766445699867</v>
+        <v>189.2564136861789</v>
       </c>
       <c r="D5" t="n">
-        <v>141.7643684932394</v>
+        <v>102.9607904828843</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.05168244208915</v>
+        <v>14.69185439405352</v>
       </c>
       <c r="C6" t="n">
-        <v>285.7465050503724</v>
+        <v>327.6887304712047</v>
       </c>
       <c r="D6" t="n">
-        <v>77.32343093418305</v>
+        <v>69.2730997593592</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>292.785636089822</v>
+        <v>333.0294379823072</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>38.92629647338602</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>199.6923917823225</v>
+        <v>182.6688865906828</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>75.88124355664445</v>
+        <v>63.89999457401638</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>22.52031058771757</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.35653864755762</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.948990177108171</v>
+        <v>0.4781111319681966</v>
       </c>
       <c r="C2" t="n">
-        <v>5.450663253978291</v>
+        <v>21.98820333201581</v>
       </c>
       <c r="D2" t="n">
-        <v>12.46328710541326</v>
+        <v>16.57779173391164</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.50608309377262</v>
+        <v>1.394081740030471</v>
       </c>
       <c r="C3" t="n">
-        <v>19.32570355809846</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D3" t="n">
-        <v>71.9032018590364</v>
+        <v>39.3680829402971</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.53217367562655</v>
+        <v>4.747731897737575</v>
       </c>
       <c r="C4" t="n">
-        <v>56.14320596276234</v>
+        <v>59.30836056125406</v>
       </c>
       <c r="D4" t="n">
-        <v>164.817768084363</v>
+        <v>97.02219861989529</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.96024103687396</v>
+        <v>13.76901155206152</v>
       </c>
       <c r="C5" t="n">
-        <v>146.746738092292</v>
+        <v>165.9889930955295</v>
       </c>
       <c r="D5" t="n">
-        <v>160.5157496443535</v>
+        <v>112.1401315175919</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.24164277509429</v>
+        <v>17.71072858461246</v>
       </c>
       <c r="C6" t="n">
-        <v>282.7678825156876</v>
+        <v>316.659776761696</v>
       </c>
       <c r="D6" t="n">
-        <v>95.67818601278141</v>
+        <v>83.60268925054564</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.5184292077671</v>
+        <v>11.37845589222053</v>
       </c>
       <c r="C7" t="n">
-        <v>344.7672135342821</v>
+        <v>401.0007402858351</v>
       </c>
       <c r="D7" t="n">
-        <v>50.66407202536089</v>
+        <v>47.90928796724435</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>271.0409061884594</v>
+        <v>301.1658344932728</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>137.8953007908027</v>
+        <v>135.6765509792049</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>51.81664383014665</v>
+        <v>46.54956739686252</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.992587986722531</v>
+        <v>4.572980806381643</v>
       </c>
       <c r="C2" t="n">
-        <v>10.38492721552276</v>
+        <v>23.12997591205485</v>
       </c>
       <c r="D2" t="n">
-        <v>5.668611244321084</v>
+        <v>5.120796025351362</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.575525138866883</v>
+        <v>0.5645049299419159</v>
       </c>
       <c r="C2" t="n">
-        <v>3.139629158181299</v>
+        <v>20.56565090856218</v>
       </c>
       <c r="D2" t="n">
-        <v>9.172468800777949</v>
+        <v>13.45387053899829</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.83068173097982</v>
+        <v>1.45298660228528</v>
       </c>
       <c r="C3" t="n">
-        <v>22.80109043113217</v>
+        <v>60.76527415435633</v>
       </c>
       <c r="D3" t="n">
-        <v>77.27336180126645</v>
+        <v>42.06788912697583</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.40975831223197</v>
+        <v>3.726714285320892</v>
       </c>
       <c r="C4" t="n">
-        <v>82.89386740807944</v>
+        <v>77.52076222273664</v>
       </c>
       <c r="D4" t="n">
-        <v>167.1788713130766</v>
+        <v>93.9080949020244</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.28186906877263</v>
+        <v>11.19192382841364</v>
       </c>
       <c r="C5" t="n">
-        <v>229.5571569455105</v>
+        <v>139.4818050808656</v>
       </c>
       <c r="D5" t="n">
-        <v>144.145106676038</v>
+        <v>119.4296082216245</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.16607959293373</v>
+        <v>18.03274183160542</v>
       </c>
       <c r="C6" t="n">
-        <v>282.4861209245688</v>
+        <v>295.9301739865246</v>
       </c>
       <c r="D6" t="n">
-        <v>75.91462297858888</v>
+        <v>95.15491448641787</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>15.15131231964102</v>
       </c>
       <c r="C7" t="n">
-        <v>190.6190794996734</v>
+        <v>424.3565181698667</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79978988825843</v>
+        <v>57.9103518304066</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="C8" t="n">
-        <v>101.6403398206723</v>
+        <v>399.4682321195058</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>35.38218726105504</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>39.49374664644068</v>
+        <v>231.5265428402295</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>89.68265278294614</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.06477965294707</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>10.39179944945249</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.167739988705962</v>
+        <v>4.698644512525235</v>
       </c>
       <c r="C2" t="n">
-        <v>4.846888415866503</v>
+        <v>12.40830923397544</v>
       </c>
       <c r="D2" t="n">
-        <v>12.15894531709675</v>
+        <v>11.12320148911636</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.7283589855599</v>
+        <v>7.37783399741478</v>
       </c>
       <c r="C3" t="n">
-        <v>26.16848505669873</v>
+        <v>45.67090320156162</v>
       </c>
       <c r="D3" t="n">
-        <v>7.898160280665589</v>
+        <v>6.562983402889927</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3982172200532</v>
+        <v>11.67701367123133</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14360779910207</v>
+        <v>59.94200351232082</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576260849418024</v>
+        <v>0.7784675780820887</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.137485736323558</v>
+        <v>3.821943812632833</v>
       </c>
       <c r="C2" t="n">
-        <v>4.331470871136927</v>
+        <v>8.637416301963437</v>
       </c>
       <c r="D2" t="n">
-        <v>18.82992096745382</v>
+        <v>13.29286391550181</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.93438713473148</v>
+        <v>13.03760951239764</v>
       </c>
       <c r="C3" t="n">
-        <v>21.622993186036</v>
+        <v>47.54604131667303</v>
       </c>
       <c r="D3" t="n">
-        <v>16.19883712007237</v>
+        <v>14.70167187109599</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.81751810019711</v>
+        <v>9.189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>40.41953473154543</v>
+        <v>73.57708169477721</v>
       </c>
       <c r="D4" t="n">
-        <v>19.20789383358884</v>
+        <v>17.59979109403257</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44095361390079</v>
+        <v>13.6242332216197</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14426753018336</v>
+        <v>73.73114449347132</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250727076610692</v>
+        <v>1.602850967249377</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.543929285881738</v>
+        <v>2.436697801940583</v>
       </c>
       <c r="C2" t="n">
-        <v>9.255917355638928</v>
+        <v>7.574183538264142</v>
       </c>
       <c r="D2" t="n">
-        <v>24.95504489424967</v>
+        <v>18.2065111752571</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.72683745850791</v>
+        <v>13.23886779176824</v>
       </c>
       <c r="C3" t="n">
-        <v>18.73174619702914</v>
+        <v>38.87230034965246</v>
       </c>
       <c r="D3" t="n">
-        <v>27.50366193447439</v>
+        <v>22.31512531753</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.32047602440774</v>
+        <v>18.71014774753571</v>
       </c>
       <c r="C4" t="n">
-        <v>48.52386203010285</v>
+        <v>101.348760752511</v>
       </c>
       <c r="D4" t="n">
-        <v>23.01118443984099</v>
+        <v>21.21164089795658</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.90998231084556</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C5" t="n">
-        <v>44.84132639147307</v>
+        <v>82.24591392327655</v>
       </c>
       <c r="D5" t="n">
-        <v>29.59969328304134</v>
+        <v>26.48264432205772</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73341752558114</v>
+        <v>14.82593091501962</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0738469060449</v>
+        <v>87.3082598328933</v>
       </c>
       <c r="D21" t="n">
-        <v>5.02002525767434</v>
+        <v>2.470988485836603</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.953318078552658</v>
+        <v>2.199114857512855</v>
       </c>
       <c r="C2" t="n">
-        <v>11.36176618124834</v>
+        <v>9.875400157018666</v>
       </c>
       <c r="D2" t="n">
-        <v>26.42275771209865</v>
+        <v>22.58216069308513</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.03608798534566</v>
+        <v>10.53906160508951</v>
       </c>
       <c r="C3" t="n">
-        <v>28.6424892714007</v>
+        <v>33.241977265797</v>
       </c>
       <c r="D3" t="n">
-        <v>40.34983064454391</v>
+        <v>31.9166178650638</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.34073287329843</v>
+        <v>22.67935371580556</v>
       </c>
       <c r="C4" t="n">
-        <v>47.60494617892783</v>
+        <v>99.07699656488386</v>
       </c>
       <c r="D4" t="n">
-        <v>31.15379989886403</v>
+        <v>27.0697294491973</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.53802310412304</v>
+        <v>18.43231314723387</v>
       </c>
       <c r="C5" t="n">
-        <v>69.01686360855078</v>
+        <v>141.0771451002667</v>
       </c>
       <c r="D5" t="n">
-        <v>30.92505268377453</v>
+        <v>28.27433388230815</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.79373517111693</v>
+        <v>8.171086142446205</v>
       </c>
       <c r="C6" t="n">
-        <v>42.58625191481815</v>
+        <v>74.90833158173589</v>
       </c>
       <c r="D6" t="n">
-        <v>37.91705983342032</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05615626642192</v>
+        <v>16.05237427098148</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7949242142763</v>
+        <v>100.5385546445682</v>
       </c>
       <c r="D21" t="n">
-        <v>6.878535720541682</v>
+        <v>3.37944721494347</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.218389958699297</v>
+        <v>1.888882582970863</v>
       </c>
       <c r="C2" t="n">
-        <v>6.261586857686157</v>
+        <v>10.32013186704247</v>
       </c>
       <c r="D2" t="n">
-        <v>25.03456645829367</v>
+        <v>30.10431160302419</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.62237129123025</v>
+        <v>8.894634200476103</v>
       </c>
       <c r="C3" t="n">
-        <v>35.49508824704343</v>
+        <v>36.01050579177301</v>
       </c>
       <c r="D3" t="n">
-        <v>48.40507055788899</v>
+        <v>41.38066573400306</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.39781310886498</v>
+        <v>21.51794618168159</v>
       </c>
       <c r="C4" t="n">
-        <v>50.48932093400496</v>
+        <v>90.44939773996289</v>
       </c>
       <c r="D4" t="n">
-        <v>38.10948238345269</v>
+        <v>35.64627739349744</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.16924582022473</v>
+        <v>25.84450831429729</v>
       </c>
       <c r="C5" t="n">
-        <v>58.83123117699012</v>
+        <v>162.8228567493335</v>
       </c>
       <c r="D5" t="n">
-        <v>28.10252803406495</v>
+        <v>31.51410130632262</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.32329809433347</v>
+        <v>16.22141731727005</v>
       </c>
       <c r="C6" t="n">
-        <v>51.88438442173969</v>
+        <v>149.21288832536</v>
       </c>
       <c r="D6" t="n">
-        <v>30.51075515258238</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>26.70942804173872</v>
+        <v>61.62332164786803</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.055082647939839</v>
+        <v>17.29569230060119</v>
       </c>
       <c r="C21" t="n">
-        <v>66.14139982443599</v>
+        <v>113.2867845689378</v>
       </c>
       <c r="D21" t="n">
-        <v>5.291311985954879</v>
+        <v>4.323923075150298</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.364670366632072</v>
+        <v>2.148063976892021</v>
       </c>
       <c r="C2" t="n">
-        <v>4.364850293081319</v>
+        <v>7.724390937013903</v>
       </c>
       <c r="D2" t="n">
-        <v>26.62008900065226</v>
+        <v>23.91046533693106</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.14055415262332</v>
+        <v>7.564366061221674</v>
       </c>
       <c r="C3" t="n">
-        <v>28.38232612977529</v>
+        <v>37.85619147575701</v>
       </c>
       <c r="D3" t="n">
-        <v>57.73658248675491</v>
+        <v>53.44143628067513</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.89854549575986</v>
+        <v>19.06750391188155</v>
       </c>
       <c r="C4" t="n">
-        <v>74.71296378859076</v>
+        <v>89.18588844459724</v>
       </c>
       <c r="D4" t="n">
-        <v>54.2670860999467</v>
+        <v>46.30314872309656</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.12769362147687</v>
+        <v>28.8879261974624</v>
       </c>
       <c r="C5" t="n">
-        <v>80.01243789611506</v>
+        <v>164.5409152317654</v>
       </c>
       <c r="D5" t="n">
-        <v>36.34920874973816</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.58747034223387</v>
+        <v>24.31200014796801</v>
       </c>
       <c r="C6" t="n">
-        <v>76.47814616082654</v>
+        <v>198.3199084917855</v>
       </c>
       <c r="D6" t="n">
-        <v>33.04660947265189</v>
+        <v>36.70951015719674</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.61800233205675</v>
+        <v>12.99539436111503</v>
       </c>
       <c r="C7" t="n">
-        <v>54.85613472249477</v>
+        <v>132.2895213995535</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>37.84833749412304</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>28.37250865273282</v>
+        <v>50.65327280061418</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>38.93905919354123</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.30869505195678</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.275592441106062</v>
+        <v>17.6649143611941</v>
       </c>
       <c r="C21" t="n">
-        <v>75.48427157647541</v>
+        <v>125.4208919644781</v>
       </c>
       <c r="D21" t="n">
-        <v>6.366143385967804</v>
+        <v>5.299474308358231</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.982369599052562</v>
+        <v>2.001783568959246</v>
       </c>
       <c r="C2" t="n">
-        <v>7.820602212030092</v>
+        <v>5.004949796250239</v>
       </c>
       <c r="D2" t="n">
-        <v>21.52089142479433</v>
+        <v>19.24421849864597</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.39719121405923</v>
+        <v>11.27046364475338</v>
       </c>
       <c r="C3" t="n">
-        <v>21.56899706230243</v>
+        <v>55.0515025156399</v>
       </c>
       <c r="D3" t="n">
-        <v>65.63474276742051</v>
+        <v>55.84671815607981</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.36549755008285</v>
+        <v>13.87307680871168</v>
       </c>
       <c r="C4" t="n">
-        <v>72.64540312344698</v>
+        <v>134.3659177940355</v>
       </c>
       <c r="D4" t="n">
-        <v>71.01177494358029</v>
+        <v>43.6612656509684</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.10439371848221</v>
+        <v>13.69538047424301</v>
       </c>
       <c r="C5" t="n">
-        <v>111.7965198211056</v>
+        <v>118.49694790259</v>
       </c>
       <c r="D5" t="n">
-        <v>47.2956956520901</v>
+        <v>32.2749557771139</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.09315252537899</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>104.4932986492135</v>
+        <v>87.10458331159403</v>
       </c>
       <c r="D6" t="n">
-        <v>37.39378830705677</v>
+        <v>24.91577498607981</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.48122060599696</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>85.39830580161305</v>
+        <v>35.57264631567892</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>52.07189823325082</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>25.62656032395449</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.482443661859187</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.17749119591586</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.482443661859187</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
